--- a/data/trans_orig/Q5408-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5408-Provincia-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>28188</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33457</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65296</t>
+          <t>64847</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>72852</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12776</t>
+          <t>12227</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58715</t>
+          <t>60454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85099</t>
+          <t>85648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95458</t>
+          <t>95770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148645</t>
+          <t>149833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160527</t>
+          <t>161311</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44656</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71043</t>
+          <t>70829</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81249</t>
+          <t>81263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119550</t>
+          <t>120379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131208</t>
+          <t>131221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>50345</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67347</t>
+          <t>69104</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>122610</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13653</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>30696</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40103</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56096</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66338</t>
+          <t>66401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>839</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15197</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17914</t>
+          <t>16759</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39823</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46345</t>
+          <t>46357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55112</t>
+          <t>56222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66895</t>
+          <t>67777</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>99592</t>
+          <t>100747</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112561</t>
+          <t>112793</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99565</t>
+          <t>100239</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108100</t>
+          <t>108857</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116221</t>
+          <t>116225</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>212013</t>
+          <t>212257</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>221249</t>
+          <t>221216</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>104108</t>
+          <t>103799</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>110964</t>
+          <t>110971</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>136509</t>
+          <t>136437</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>149381</t>
+          <t>149545</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>244933</t>
+          <t>244667</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>259359</t>
+          <t>259391</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>46508</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>36346</t>
+          <t>34743</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>63735</t>
+          <t>63138</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>474144</t>
+          <t>474315</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>490459</t>
+          <t>489966</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>624222</t>
+          <t>625202</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>650411</t>
+          <t>649307</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1107294</t>
+          <t>1108311</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1136691</t>
+          <t>1137175</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33702</t>
+          <t>33620</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46758</t>
+          <t>46707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75012</t>
+          <t>75550</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88024</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>14405</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64975</t>
+          <t>65016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77058</t>
+          <t>77094</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80643</t>
+          <t>81578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96272</t>
+          <t>96208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151785</t>
+          <t>152196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170253</t>
+          <t>170761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>11949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45297</t>
+          <t>45123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53765</t>
+          <t>53807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61327</t>
+          <t>61682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74514</t>
+          <t>74484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111083</t>
+          <t>110262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126111</t>
+          <t>126004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56563</t>
+          <t>57333</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78016</t>
+          <t>79134</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>139624</t>
+          <t>138910</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>148477</t>
+          <t>148439</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>23409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30633</t>
+          <t>30615</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39354</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47859</t>
+          <t>47873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>66096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77413</t>
+          <t>78132</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14962</t>
+          <t>15184</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43207</t>
+          <t>43225</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50694</t>
+          <t>50697</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56648</t>
+          <t>56500</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>66922</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>104118</t>
+          <t>103519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116600</t>
+          <t>116635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22679</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>94924</t>
+          <t>96529</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109299</t>
+          <t>109228</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>121620</t>
+          <t>121910</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>135127</t>
+          <t>135581</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>224661</t>
+          <t>223750</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>242752</t>
+          <t>242120</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19013</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>109560</t>
+          <t>110291</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>119614</t>
+          <t>119651</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>147441</t>
+          <t>146347</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>159904</t>
+          <t>160044</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>259367</t>
+          <t>261672</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>277321</t>
+          <t>277273</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>30792</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>44466</t>
+          <t>43129</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>33164</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>63580</t>
+          <t>60314</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>56470</t>
+          <t>55928</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>91430</t>
+          <t>91242</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>509512</t>
+          <t>509255</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>533224</t>
+          <t>532930</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>657950</t>
+          <t>661567</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>691615</t>
+          <t>694105</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1176887</t>
+          <t>1179295</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1218235</t>
+          <t>1218334</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37319</t>
+          <t>37342</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42351</t>
+          <t>41426</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76563</t>
+          <t>75494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85514</t>
+          <t>85566</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>20341</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80873</t>
+          <t>80860</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97835</t>
+          <t>97526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111223</t>
+          <t>111200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181551</t>
+          <t>180845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197183</t>
+          <t>197244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53314</t>
+          <t>55082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62315</t>
+          <t>62441</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78652</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127429</t>
+          <t>127796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139899</t>
+          <t>139750</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>804</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55288</t>
+          <t>55978</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63417</t>
+          <t>63410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82648</t>
+          <t>83626</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>143081</t>
+          <t>143138</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>154026</t>
+          <t>154125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>42196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49428</t>
+          <t>49415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82528</t>
+          <t>83143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91508</t>
+          <t>91473</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14149</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19496</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>39349</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46787</t>
+          <t>46817</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48853</t>
+          <t>48755</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61713</t>
+          <t>62386</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91220</t>
+          <t>91119</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>106378</t>
+          <t>106751</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>872</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99470</t>
+          <t>99775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>109379</t>
+          <t>109470</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>131804</t>
+          <t>129445</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>143865</t>
+          <t>143829</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>236359</t>
+          <t>235497</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>251605</t>
+          <t>251347</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>17962</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>125669</t>
+          <t>125514</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>133305</t>
+          <t>133306</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>161710</t>
+          <t>161414</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>173683</t>
+          <t>173688</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>291167</t>
+          <t>292050</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>305932</t>
+          <t>305360</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>24655</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>30102</t>
+          <t>30054</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>34446</t>
+          <t>34177</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>50311</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>44853</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>75287</t>
+          <t>74996</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>550407</t>
+          <t>551194</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>570953</t>
+          <t>571412</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>711792</t>
+          <t>713049</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>743047</t>
+          <t>742614</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1271483</t>
+          <t>1272896</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1308108</t>
+          <t>1308889</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>723</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -13871,12 +13871,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13896,32 +13896,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13931,32 +13931,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -13974,27 +13974,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55185</t>
+          <t>60232</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52401</t>
+          <t>56668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -14009,32 +14009,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58573</t>
+          <t>60525</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53830</t>
+          <t>56723</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61395</t>
+          <t>63086</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14044,32 +14044,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>113758</t>
+          <t>120757</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108412</t>
+          <t>116551</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116654</t>
+          <t>123849</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -14087,17 +14087,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14239,32 +14239,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14274,32 +14274,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -14317,32 +14317,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14352,32 +14352,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>14535</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24944</t>
+          <t>27920</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -14430,32 +14430,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>76324</t>
+          <t>83712</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70903</t>
+          <t>78154</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79043</t>
+          <t>86544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14465,32 +14465,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>111311</t>
+          <t>116354</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103901</t>
+          <t>108786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116758</t>
+          <t>122070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14500,32 +14500,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>187635</t>
+          <t>200066</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178456</t>
+          <t>191252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194097</t>
+          <t>206859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14578,17 +14578,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14613,17 +14613,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14660,32 +14660,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14695,32 +14695,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14730,32 +14730,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7435</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -14773,32 +14773,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14808,32 +14808,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14843,32 +14843,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15392</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21760</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -14886,32 +14886,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>65996</t>
+          <t>64897</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61129</t>
+          <t>60313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69201</t>
+          <t>68075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14921,32 +14921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>75581</t>
+          <t>74014</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70072</t>
+          <t>68878</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79790</t>
+          <t>77823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14956,32 +14956,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>141577</t>
+          <t>138912</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134784</t>
+          <t>132410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>146744</t>
+          <t>144053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -14999,17 +14999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15151,32 +15151,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>464</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15186,32 +15186,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>644</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15264,32 +15264,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15299,32 +15299,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -15342,27 +15342,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73999</t>
+          <t>82512</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71395</t>
+          <t>79887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -15377,32 +15377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98879</t>
+          <t>105598</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>95424</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101120</t>
+          <t>107947</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15412,32 +15412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>172877</t>
+          <t>188110</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>169381</t>
+          <t>184310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>190634</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15490,17 +15490,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>888</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -15617,12 +15617,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>888</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -15685,32 +15685,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15755,32 +15755,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -15798,32 +15798,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>31380</t>
+          <t>32960</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27952</t>
+          <t>29992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>35012</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15833,32 +15833,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52591</t>
+          <t>54545</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48921</t>
+          <t>50660</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55142</t>
+          <t>57203</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15868,32 +15868,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>83971</t>
+          <t>87505</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79347</t>
+          <t>82915</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87316</t>
+          <t>91282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -15911,17 +15911,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15981,17 +15981,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16098,32 +16098,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -16151,12 +16151,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -16186,22 +16186,22 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9728</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16211,32 +16211,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -16254,32 +16254,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>55851</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52629</t>
+          <t>52807</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57980</t>
+          <t>58025</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>54839</t>
+          <t>56685</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51066</t>
+          <t>52894</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58363</t>
+          <t>60207</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16324,17 +16324,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>110756</t>
+          <t>112534</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106249</t>
+          <t>107966</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114673</t>
+          <t>116496</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -16367,17 +16367,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16402,17 +16402,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -16494,12 +16494,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16519,32 +16519,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16554,32 +16554,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>875</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -16607,12 +16607,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16632,32 +16632,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16667,32 +16667,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -16710,27 +16710,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>121380</t>
+          <t>149132</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117102</t>
+          <t>143736</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -16745,32 +16745,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>327946</t>
+          <t>151484</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>307647</t>
+          <t>144675</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>336029</t>
+          <t>156037</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16780,32 +16780,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>449326</t>
+          <t>300617</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>436018</t>
+          <t>292755</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>458538</t>
+          <t>305992</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -16823,17 +16823,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16858,17 +16858,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>338603</t>
+          <t>164081</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>338603</t>
+          <t>164081</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>338603</t>
+          <t>164081</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>461857</t>
+          <t>315422</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>461857</t>
+          <t>315422</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>461857</t>
+          <t>315422</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -16950,12 +16950,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -17020,12 +17020,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -17053,32 +17053,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17088,32 +17088,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17123,32 +17123,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -17166,32 +17166,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>145089</t>
+          <t>160888</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>142007</t>
+          <t>156843</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>146465</t>
+          <t>162882</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17201,32 +17201,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>180983</t>
+          <t>205892</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>176146</t>
+          <t>199955</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>183929</t>
+          <t>209465</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17236,32 +17236,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>326071</t>
+          <t>366781</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>320027</t>
+          <t>359738</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>329598</t>
+          <t>371009</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -17279,17 +17279,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17314,17 +17314,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17349,17 +17349,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17396,17 +17396,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -17431,32 +17431,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23940</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17466,32 +17466,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>17302</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -17509,32 +17509,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>19580</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>28006</t>
+          <t>28647</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17544,32 +17544,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>56378</t>
+          <t>59852</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>29721</t>
+          <t>47981</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>76099</t>
+          <t>71184</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17579,32 +17579,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>75958</t>
+          <t>80167</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>49871</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>93261</t>
+          <t>94457</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -17622,32 +17622,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>625269</t>
+          <t>690184</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>616380</t>
+          <t>681014</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>631884</t>
+          <t>697588</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17657,32 +17657,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>960703</t>
+          <t>825096</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>936266</t>
+          <t>813081</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>995017</t>
+          <t>838237</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17692,32 +17692,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1585972</t>
+          <t>1515280</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1565004</t>
+          <t>1499223</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1618603</t>
+          <t>1528316</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -17735,17 +17735,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17770,17 +17770,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1033211</t>
+          <t>902655</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1033211</t>
+          <t>902655</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1033211</t>
+          <t>902655</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17805,17 +17805,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1683389</t>
+          <t>1619046</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1683389</t>
+          <t>1619046</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1683389</t>
+          <t>1619046</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
